--- a/data/trans_bre/IP04D$notiene-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$notiene-Clase-trans_bre.xlsx
@@ -632,17 +632,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 7,86</t>
+          <t>0,34; 7,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 4,04</t>
+          <t>-9,58; 4,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,44; -0,59</t>
+          <t>-22,37; -0,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -652,12 +652,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-66,4; 68,2</t>
+          <t>-69,03; 70,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-81,38; 1,27</t>
+          <t>-82,26; -4,71</t>
         </is>
       </c>
     </row>
@@ -712,17 +712,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 1,49</t>
+          <t>-6,35; 0,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 4,45</t>
+          <t>-7,07; 5,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 11,49</t>
+          <t>-5,9; 10,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,07; 87,01</t>
+          <t>-61,82; 92,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,69; 187,21</t>
+          <t>-40,33; 160,8</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 4,95</t>
+          <t>-4,75; 4,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 2,93</t>
+          <t>-13,99; 3,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 19,51</t>
+          <t>-7,69; 17,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-82,05; 497,8</t>
+          <t>-83,44; 423,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-82,84; 48,43</t>
+          <t>-82,07; 70,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,64; 218,28</t>
+          <t>-41,2; 225,09</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 0,89</t>
+          <t>-5,8; 0,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 4,7</t>
+          <t>-6,62; 5,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 12,84</t>
+          <t>-4,57; 12,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-76,86; 29,29</t>
+          <t>-77,41; 38,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,71; 36,58</t>
+          <t>-34,47; 38,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,21; 123,98</t>
+          <t>-33,42; 128,94</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 6,68</t>
+          <t>-2,06; 7,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 4,68</t>
+          <t>-9,96; 4,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 8,12</t>
+          <t>-7,62; 8,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-40,02; 261,52</t>
+          <t>-39,33; 293,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,98; 34,8</t>
+          <t>-46,43; 33,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-43,03; 74,46</t>
+          <t>-39,38; 73,48</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 11,62</t>
+          <t>-0,84; 12,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 8,05</t>
+          <t>-13,98; 8,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 6,62</t>
+          <t>-13,32; 6,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1052,12 +1052,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-52,08; 53,67</t>
+          <t>-51,17; 63,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-76,83; 106,47</t>
+          <t>-77,32; 102,38</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,74</t>
+          <t>-1,56; 1,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 1,01</t>
+          <t>-4,72; 1,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 3,98</t>
+          <t>-4,1; 4,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-37,47; 59,46</t>
+          <t>-33,84; 58,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-29,1; 7,68</t>
+          <t>-28,93; 9,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,83; 34,94</t>
+          <t>-26,54; 37,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$notiene-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$notiene-Clase-trans_bre.xlsx
@@ -632,17 +632,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 7,82</t>
+          <t>-0,0; 7,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 4,48</t>
+          <t>-8,43; 4,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,37; -0,76</t>
+          <t>-21,59; -0,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -652,12 +652,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-69,03; 70,91</t>
+          <t>-65,98; 67,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-82,26; -4,71</t>
+          <t>-81,33; 1,84</t>
         </is>
       </c>
     </row>
@@ -712,17 +712,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 0,94</t>
+          <t>-5,9; 1,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 5,25</t>
+          <t>-7,63; 4,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 10,86</t>
+          <t>-5,22; 10,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,82; 92,17</t>
+          <t>-63,18; 88,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,33; 160,8</t>
+          <t>-38,3; 159,17</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 4,71</t>
+          <t>-5,83; 4,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 3,48</t>
+          <t>-13,75; 2,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 17,49</t>
+          <t>-7,45; 18,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-83,44; 423,02</t>
+          <t>-83,21; 432,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-82,07; 70,1</t>
+          <t>-81,34; 60,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,2; 225,09</t>
+          <t>-40,63; 248,64</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 0,71</t>
+          <t>-5,65; 0,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 5,0</t>
+          <t>-6,09; 5,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 12,58</t>
+          <t>-4,38; 11,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-77,41; 38,69</t>
+          <t>-76,64; 24,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,47; 38,74</t>
+          <t>-32,35; 41,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,42; 128,94</t>
+          <t>-32,58; 120,08</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 7,05</t>
+          <t>-2,33; 6,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 4,56</t>
+          <t>-10,39; 4,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 8,52</t>
+          <t>-7,94; 8,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-39,33; 293,58</t>
+          <t>-38,77; 260,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-46,43; 33,3</t>
+          <t>-48,67; 34,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,38; 73,48</t>
+          <t>-41,13; 81,55</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 12,0</t>
+          <t>-0,81; 10,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 8,75</t>
+          <t>-16,27; 7,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 6,29</t>
+          <t>-13,53; 7,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1052,12 +1052,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-51,17; 63,93</t>
+          <t>-55,95; 51,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,32; 102,38</t>
+          <t>-78,44; 142,42</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,81</t>
+          <t>-1,44; 1,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 1,23</t>
+          <t>-4,64; 1,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 4,32</t>
+          <t>-4,19; 4,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-33,84; 58,06</t>
+          <t>-34,37; 68,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-28,93; 9,42</t>
+          <t>-28,81; 10,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,54; 37,58</t>
+          <t>-26,11; 35,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$notiene-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$notiene-Clase-trans_bre.xlsx
@@ -518,8 +518,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no dispone de calefacción en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -604,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-9,06</t>
+          <t>-3,86</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-53,3%</t>
+          <t>-33,22%</t>
         </is>
       </c>
     </row>
@@ -632,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 7,57</t>
+          <t>0,48; 7,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 4,03</t>
+          <t>-9,34; 4,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,59; -0,53</t>
+          <t>-10,51; 3,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -652,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-65,98; 67,2</t>
+          <t>-66,4; 68,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-81,33; 1,84</t>
+          <t>-68,46; 39,73</t>
         </is>
       </c>
     </row>
@@ -684,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>2,9</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -699,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -712,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 1,24</t>
+          <t>-6,33; 1,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 4,8</t>
+          <t>-7,06; 4,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 10,81</t>
+          <t>-5,69; 11,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -732,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,18; 88,77</t>
+          <t>-59,07; 87,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,3; 159,17</t>
+          <t>-38,82; 182,68</t>
         </is>
       </c>
     </row>
@@ -764,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,31</t>
+          <t>7,8</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>69,6%</t>
         </is>
       </c>
     </row>
@@ -792,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 4,15</t>
+          <t>-4,76; 4,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 2,9</t>
+          <t>-13,58; 2,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 18,26</t>
+          <t>-2,71; 20,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-83,21; 432,11</t>
+          <t>-82,05; 497,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-81,34; 60,71</t>
+          <t>-82,84; 48,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-40,63; 248,64</t>
+          <t>-21,98; 297,63</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -872,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 0,71</t>
+          <t>-5,53; 0,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 5,35</t>
+          <t>-6,16; 4,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 11,51</t>
+          <t>-5,12; 5,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-76,64; 24,9</t>
+          <t>-76,86; 29,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,35; 41,3</t>
+          <t>-31,71; 36,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,58; 120,08</t>
+          <t>-33,55; 65,07</t>
         </is>
       </c>
     </row>
@@ -924,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -939,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -952,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 6,5</t>
+          <t>-2,16; 6,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 4,64</t>
+          <t>-10,1; 4,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 8,74</t>
+          <t>-6,44; 8,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-38,77; 260,73</t>
+          <t>-40,02; 261,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-48,67; 34,36</t>
+          <t>-45,98; 34,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-41,13; 81,55</t>
+          <t>-36,93; 90,04</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-3,27</t>
+          <t>-5,81</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1019,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-27,27%</t>
+          <t>-48,26%</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 10,71</t>
+          <t>-0,83; 11,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 7,7</t>
+          <t>-14,02; 8,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 7,47</t>
+          <t>-16,69; 1,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1052,12 +1054,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,95; 51,74</t>
+          <t>-52,08; 53,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-78,44; 142,42</t>
+          <t>-82,92; 35,68</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1099,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,66%</t>
+          <t>0,07%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,95</t>
+          <t>-1,75; 1,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 1,29</t>
+          <t>-4,71; 1,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 4,3</t>
+          <t>-3,28; 3,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-34,37; 68,63</t>
+          <t>-37,47; 59,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-28,81; 10,06</t>
+          <t>-29,1; 7,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 35,94</t>
+          <t>-23,67; 29,15</t>
         </is>
       </c>
     </row>
